--- a/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
+++ b/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Ranking_2026" sheetId="2" r:id="rId2"/>
     <sheet name="Visitados_2026" sheetId="3" r:id="rId3"/>
     <sheet name="Laboratorio_2026" sheetId="4" r:id="rId4"/>
+    <sheet name="Producao_2025" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,9 +443,25 @@
         <v>Use numero de 1 a 12 ou nome do mes. Mantenha Ano = 2026.</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Producao_2025</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Opcional. Informe a producao total de 2025 por medico e mes para comparar com 2026.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Comparativo 2025 x 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Use a aba Producao_2025 com Ano = 2025. O dashboard compara o mesmo mes selecionado em 2026 contra 2025.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -861,4 +878,99 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Mes Producao</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Medico Solicitante</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Producao</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D2">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dr. Santos</v>
+      </c>
+      <c r="D5">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dra. Costa</v>
+      </c>
+      <c r="D6">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
+++ b/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
@@ -448,7 +448,7 @@
         <v>Producao_2025</v>
       </c>
       <c r="B6" t="str">
-        <v>Opcional. Informe a producao total de 2025 por medico e mes para comparar com 2026.</v>
+        <v>Opcional. Mesmo formato de Visitados_2026: informe a producao de imagem de 2025 separada por Cintilografia, Densitometria, Mamografia, Ressonancia, Tomografia e Ultrassom.</v>
       </c>
     </row>
     <row r="7">
@@ -456,7 +456,7 @@
         <v>Comparativo 2025 x 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>Use a aba Producao_2025 com Ano = 2025. O dashboard compara o mesmo mes selecionado em 2026 contra 2025.</v>
+        <v>O dashboard compara Producao_2025 contra Visitados_2026, usando as mesmas modalidades de imagem.</v>
       </c>
     </row>
   </sheetData>
@@ -882,20 +882,47 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Ano</v>
       </c>
       <c r="B1" t="str">
+        <v>Mes Visita</v>
+      </c>
+      <c r="C1" t="str">
         <v>Mes Producao</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Medico Solicitante</v>
       </c>
-      <c r="D1" t="str">
-        <v>Producao</v>
+      <c r="E1" t="str">
+        <v>Representante</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Especialidade</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Cintilografia</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Densitometria</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Mamografia</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Ressonancia</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Tomografia</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Ultrassom</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Total</v>
       </c>
     </row>
     <row r="2">
@@ -905,11 +932,38 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
         <v>Dra. Almeida</v>
       </c>
-      <c r="D2">
-        <v>820</v>
+      <c r="E2" t="str">
+        <v>Renata</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Cardiologia</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>38</v>
+      </c>
+      <c r="K2">
+        <v>76</v>
+      </c>
+      <c r="L2">
+        <v>61</v>
+      </c>
+      <c r="M2">
+        <v>221</v>
       </c>
     </row>
     <row r="3">
@@ -919,11 +973,38 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="str">
-        <v>Dra. Almeida</v>
-      </c>
-      <c r="D3">
-        <v>860</v>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Dr. Santos</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Marcos</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Ortopedia</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>45</v>
+      </c>
+      <c r="K3">
+        <v>82</v>
+      </c>
+      <c r="L3">
+        <v>35</v>
+      </c>
+      <c r="M3">
+        <v>180</v>
       </c>
     </row>
     <row r="4">
@@ -933,44 +1014,43 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="str">
-        <v>Dra. Almeida</v>
-      </c>
-      <c r="D4">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>2025</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Dr. Santos</v>
-      </c>
-      <c r="D5">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>2025</v>
-      </c>
-      <c r="B6">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D4" t="str">
         <v>Dra. Costa</v>
       </c>
-      <c r="D6">
-        <v>540</v>
+      <c r="E4" t="str">
+        <v>Renata</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Clinica Medica</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>67</v>
+      </c>
+      <c r="L4">
+        <v>49</v>
+      </c>
+      <c r="M4">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
+++ b/ranking-solicitantes-visitas-2026-html/modelo_ranking_solicitantes_visitas_2026.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Visitados_2026" sheetId="3" r:id="rId3"/>
     <sheet name="Laboratorio_2026" sheetId="4" r:id="rId4"/>
     <sheet name="Producao_2025" sheetId="5" r:id="rId5"/>
+    <sheet name="Laboratorio_2025" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -453,15 +454,23 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Laboratorio_2025</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Opcional. Mesmo formato de Laboratorio_2026: informe a producao de laboratorio de 2025 por medico e mes.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>Comparativo 2025 x 2026</v>
       </c>
-      <c r="B7" t="str">
-        <v>O dashboard compara Producao_2025 contra Visitados_2026, usando as mesmas modalidades de imagem.</v>
+      <c r="B8" t="str">
+        <v>O dashboard compara Producao_2025 contra Visitados_2026 por modalidade e Laboratorio_2025 contra Laboratorio_2026.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1053,4 +1062,99 @@
     <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Mes Producao</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Medico Solicitante</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Producao</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dra. Almeida</v>
+      </c>
+      <c r="D4">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Dr. Santos</v>
+      </c>
+      <c r="D5">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dra. Costa</v>
+      </c>
+      <c r="D6">
+        <v>510</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+  </ignoredErrors>
+</worksheet>
 </file>